--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53257083146988</v>
+        <v>2.361542760113856</v>
       </c>
       <c r="D2" t="n">
-        <v>48.61222355254868</v>
+        <v>7.899486327289161</v>
       </c>
       <c r="E2" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F2" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.94998190651774</v>
+        <v>1.779372059809133</v>
       </c>
       <c r="D3" t="n">
-        <v>11.33056395947445</v>
+        <v>1.841216643414599</v>
       </c>
       <c r="E3" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.13450026707068</v>
+        <v>6.684356293398985</v>
       </c>
       <c r="D4" t="n">
-        <v>65.30513114543106</v>
+        <v>10.61208381113255</v>
       </c>
       <c r="E4" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F4" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.29763590546858</v>
+        <v>4.110865834638644</v>
       </c>
       <c r="D5" t="n">
-        <v>45.01364642730972</v>
+        <v>7.31471754443783</v>
       </c>
       <c r="E5" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F5" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.14477937307737</v>
+        <v>3.761026648125072</v>
       </c>
       <c r="D6" t="n">
-        <v>30.90389828408007</v>
+        <v>5.021883471163012</v>
       </c>
       <c r="E6" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F6" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.89957120944451</v>
+        <v>4.046180321534733</v>
       </c>
       <c r="D7" t="n">
-        <v>27.87370730191998</v>
+        <v>4.529477436561996</v>
       </c>
       <c r="E7" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F7" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.09930649238177</v>
+        <v>4.891137305012037</v>
       </c>
       <c r="D8" t="n">
-        <v>30.16002288688518</v>
+        <v>4.901003719118843</v>
       </c>
       <c r="E8" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F8" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.38702020156161</v>
+        <v>3.800390782753762</v>
       </c>
       <c r="D9" t="n">
-        <v>18.09774963341383</v>
+        <v>2.940884315429748</v>
       </c>
       <c r="E9" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F9" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91946507222275</v>
+        <v>3.724413074236197</v>
       </c>
       <c r="D10" t="n">
-        <v>22.66389426759608</v>
+        <v>3.682882818484363</v>
       </c>
       <c r="E10" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F10" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.66069041607939</v>
+        <v>5.632362192612901</v>
       </c>
       <c r="D11" t="n">
-        <v>34.89924738117534</v>
+        <v>5.671127699440993</v>
       </c>
       <c r="E11" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F11" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.94265175504352</v>
+        <v>6.978180910194572</v>
       </c>
       <c r="D12" t="n">
-        <v>43.18947606912271</v>
+        <v>7.018289861232441</v>
       </c>
       <c r="E12" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F12" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.29624335054191</v>
+        <v>6.060639544463061</v>
       </c>
       <c r="D13" t="n">
-        <v>40.15159579634589</v>
+        <v>6.524634316906208</v>
       </c>
       <c r="E13" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F13" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.80552678355282</v>
+        <v>6.468398102327334</v>
       </c>
       <c r="D14" t="n">
-        <v>52.07047398902515</v>
+        <v>8.461452023216587</v>
       </c>
       <c r="E14" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F14" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.71100191060527</v>
+        <v>8.240537810473356</v>
       </c>
       <c r="D15" t="n">
-        <v>50.92982855201807</v>
+        <v>8.276097139702935</v>
       </c>
       <c r="E15" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F15" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.2009738576665</v>
+        <v>5.720158251870807</v>
       </c>
       <c r="D16" t="n">
-        <v>33.7489066745408</v>
+        <v>5.48419733461288</v>
       </c>
       <c r="E16" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F16" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.40598078366838</v>
+        <v>3.478471877346111</v>
       </c>
       <c r="D17" t="n">
-        <v>20.85179396742179</v>
+        <v>3.388416519706042</v>
       </c>
       <c r="E17" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F17" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>31.76517419921889</v>
+        <v>5.161840807373069</v>
       </c>
       <c r="D18" t="n">
-        <v>30.58977227539332</v>
+        <v>4.970837994751414</v>
       </c>
       <c r="E18" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F18" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.39446582193068</v>
+        <v>3.151600696063736</v>
       </c>
       <c r="D19" t="n">
-        <v>17.51729070270161</v>
+        <v>2.846559739189011</v>
       </c>
       <c r="E19" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F19" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>11.19364440852801</v>
+        <v>1.818967216385801</v>
       </c>
       <c r="D20" t="n">
-        <v>10.99647716775653</v>
+        <v>1.786927539760436</v>
       </c>
       <c r="E20" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F20" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>29.81319548163048</v>
+        <v>4.844644265764953</v>
       </c>
       <c r="D21" t="n">
-        <v>27.93589682419045</v>
+        <v>4.539583233930949</v>
       </c>
       <c r="E21" t="n">
-        <v>10.51081158485946</v>
+        <v>1.708006882539661</v>
       </c>
       <c r="F21" t="n">
-        <v>14.16987052559833</v>
+        <v>2.302603960409729</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
